--- a/recommendation_forms/011_trail_camera_battery_recommendation_form--recommendation_forms.xlsx
+++ b/recommendation_forms/011_trail_camera_battery_recommendation_form--recommendation_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -987,8 +987,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1016,12 +1016,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'urban'}</t>
+          <t>urban</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Urban'}</t>
+          <t>Urban</t>
         </is>
       </c>
     </row>
@@ -1033,12 +1033,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'rural'}</t>
+          <t>rural</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Rural'}</t>
+          <t>Rural</t>
         </is>
       </c>
     </row>
@@ -1050,12 +1050,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'both'}</t>
+          <t>both</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Both'}</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
@@ -1067,12 +1067,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'forest'}</t>
+          <t>forest</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Forest'}</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -1084,12 +1084,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'mountain'}</t>
+          <t>mountain</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Mountain'}</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -1101,12 +1101,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'waterfront'}</t>
+          <t>waterfront</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Waterfront'}</t>
+          <t>Waterfront</t>
         </is>
       </c>
     </row>
@@ -1118,12 +1118,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'24_hours'}</t>
+          <t>24_hours</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': '24 Hours'}</t>
+          <t>24 Hours</t>
         </is>
       </c>
     </row>
@@ -1135,12 +1135,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'48_hours'}</t>
+          <t>48_hours</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': '48 Hours'}</t>
+          <t>48 Hours</t>
         </is>
       </c>
     </row>
@@ -1152,12 +1152,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'72_hours'}</t>
+          <t>72_hours</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': '72 Hours'}</t>
+          <t>72 Hours</t>
         </is>
       </c>
     </row>
@@ -1169,12 +1169,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'aa'}</t>
+          <t>aa</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'AA'}</t>
+          <t>AA</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'d'}</t>
+          <t>d</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'D'}</t>
+          <t>D</t>
         </is>
       </c>
     </row>
@@ -1203,12 +1203,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'9v'}</t>
+          <t>9v</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': '9V'}</t>
+          <t>9V</t>
         </is>
       </c>
     </row>
